--- a/util/Analysis/BadSmells/ShotgunSurgery/ShotgunSurgerySmellRelationAnalysisOfmodels.xlsx
+++ b/util/Analysis/BadSmells/ShotgunSurgery/ShotgunSurgerySmellRelationAnalysisOfmodels.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11010"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neda/Documents/workspace/DissertationProject/util/Analysis/BadSmells/ShotgunSurgery/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/neda/Documents/PycharmProjects/DissertationProject/util/Analysis/BadSmells/ShotgunSurgery/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBE5E854-3358-BB43-9246-DB85714D5461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3BD0F0-1941-1144-AAB2-A495563653ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80" yWindow="460" windowWidth="25440" windowHeight="14000"/>
+    <workbookView xWindow="80" yWindow="460" windowWidth="25440" windowHeight="14000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ShotgunSurgerySmellRelationAnal" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ShotgunSurgerySmellRelationAnal!$A$1:$I$252</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -430,7 +433,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -1264,7 +1267,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I252"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -1297,7 +1301,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1326,7 +1330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1355,7 +1359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1384,7 +1388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1413,7 +1417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1442,7 +1446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -1471,7 +1475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1500,7 +1504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1529,7 +1533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1558,7 +1562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1587,7 +1591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -1616,7 +1620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -1645,7 +1649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -1674,7 +1678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -1703,7 +1707,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -1732,7 +1736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1761,7 +1765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -1790,7 +1794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -1819,7 +1823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -1848,7 +1852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -1877,7 +1881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -1906,7 +1910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -1935,7 +1939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -1964,7 +1968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -1993,7 +1997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -2022,7 +2026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -2051,7 +2055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -2080,7 +2084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -2109,7 +2113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -2138,7 +2142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -2167,7 +2171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -2196,7 +2200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -2225,7 +2229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -2254,7 +2258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -2283,7 +2287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -2312,7 +2316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -2341,7 +2345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -2370,7 +2374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>47</v>
       </c>
@@ -2399,7 +2403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>48</v>
       </c>
@@ -2428,7 +2432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -2457,7 +2461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>31</v>
       </c>
@@ -2486,7 +2490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>32</v>
       </c>
@@ -2515,7 +2519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>33</v>
       </c>
@@ -2544,7 +2548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>34</v>
       </c>
@@ -2573,7 +2577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>35</v>
       </c>
@@ -2602,7 +2606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>40</v>
       </c>
@@ -2631,7 +2635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>41</v>
       </c>
@@ -2660,7 +2664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>42</v>
       </c>
@@ -2689,7 +2693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>43</v>
       </c>
@@ -2718,7 +2722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>44</v>
       </c>
@@ -2747,7 +2751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>49</v>
       </c>
@@ -2776,7 +2780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>50</v>
       </c>
@@ -2805,7 +2809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>50</v>
       </c>
@@ -2834,7 +2838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>51</v>
       </c>
@@ -2863,7 +2867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>52</v>
       </c>
@@ -2892,7 +2896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>53</v>
       </c>
@@ -2921,7 +2925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>54</v>
       </c>
@@ -2950,7 +2954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>55</v>
       </c>
@@ -2979,7 +2983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>56</v>
       </c>
@@ -3008,7 +3012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>57</v>
       </c>
@@ -3037,7 +3041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>58</v>
       </c>
@@ -3066,7 +3070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>59</v>
       </c>
@@ -3095,7 +3099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>60</v>
       </c>
@@ -3124,7 +3128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>61</v>
       </c>
@@ -3153,7 +3157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>61</v>
       </c>
@@ -3182,7 +3186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>61</v>
       </c>
@@ -3211,7 +3215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>62</v>
       </c>
@@ -3240,7 +3244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>63</v>
       </c>
@@ -3269,7 +3273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>9</v>
       </c>
@@ -3298,7 +3302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>11</v>
       </c>
@@ -3327,7 +3331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>12</v>
       </c>
@@ -3356,7 +3360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>13</v>
       </c>
@@ -3385,7 +3389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>14</v>
       </c>
@@ -3414,7 +3418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>15</v>
       </c>
@@ -3443,7 +3447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>64</v>
       </c>
@@ -3472,7 +3476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>65</v>
       </c>
@@ -3501,7 +3505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>66</v>
       </c>
@@ -3530,7 +3534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>11</v>
       </c>
@@ -3559,7 +3563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>12</v>
       </c>
@@ -3588,7 +3592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>13</v>
       </c>
@@ -3617,7 +3621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>14</v>
       </c>
@@ -3646,7 +3650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>15</v>
       </c>
@@ -3675,7 +3679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>16</v>
       </c>
@@ -3704,7 +3708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>17</v>
       </c>
@@ -3733,7 +3737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>15</v>
       </c>
@@ -3762,7 +3766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>67</v>
       </c>
@@ -3791,7 +3795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>68</v>
       </c>
@@ -3820,7 +3824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>69</v>
       </c>
@@ -3849,7 +3853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>70</v>
       </c>
@@ -3878,7 +3882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>71</v>
       </c>
@@ -3907,7 +3911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>72</v>
       </c>
@@ -3936,7 +3940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>73</v>
       </c>
@@ -3965,7 +3969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>74</v>
       </c>
@@ -3994,7 +3998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>47</v>
       </c>
@@ -4023,7 +4027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>48</v>
       </c>
@@ -4052,7 +4056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>11</v>
       </c>
@@ -4081,7 +4085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>12</v>
       </c>
@@ -4110,7 +4114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>13</v>
       </c>
@@ -4139,7 +4143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>14</v>
       </c>
@@ -4168,7 +4172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>15</v>
       </c>
@@ -4197,7 +4201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>75</v>
       </c>
@@ -4226,7 +4230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>76</v>
       </c>
@@ -4255,7 +4259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>11</v>
       </c>
@@ -4284,7 +4288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>77</v>
       </c>
@@ -4313,7 +4317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>78</v>
       </c>
@@ -4342,7 +4346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>78</v>
       </c>
@@ -4371,7 +4375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>79</v>
       </c>
@@ -4400,7 +4404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>80</v>
       </c>
@@ -4429,7 +4433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>80</v>
       </c>
@@ -4458,7 +4462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>81</v>
       </c>
@@ -4487,7 +4491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>15</v>
       </c>
@@ -4516,7 +4520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>47</v>
       </c>
@@ -4545,7 +4549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>48</v>
       </c>
@@ -4574,7 +4578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -4603,7 +4607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>31</v>
       </c>
@@ -4632,7 +4636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>32</v>
       </c>
@@ -4661,7 +4665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>33</v>
       </c>
@@ -4690,7 +4694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>34</v>
       </c>
@@ -4719,7 +4723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>35</v>
       </c>
@@ -4748,7 +4752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>40</v>
       </c>
@@ -4777,7 +4781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>41</v>
       </c>
@@ -4806,7 +4810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>42</v>
       </c>
@@ -4835,7 +4839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>43</v>
       </c>
@@ -4864,7 +4868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>44</v>
       </c>
@@ -4893,7 +4897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>49</v>
       </c>
@@ -4922,7 +4926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>50</v>
       </c>
@@ -4951,7 +4955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>50</v>
       </c>
@@ -4980,7 +4984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>51</v>
       </c>
@@ -5009,7 +5013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>52</v>
       </c>
@@ -5038,7 +5042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>53</v>
       </c>
@@ -5067,7 +5071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>54</v>
       </c>
@@ -5096,7 +5100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>55</v>
       </c>
@@ -5125,7 +5129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>56</v>
       </c>
@@ -5154,7 +5158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>57</v>
       </c>
@@ -5183,7 +5187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>58</v>
       </c>
@@ -5212,7 +5216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>59</v>
       </c>
@@ -5241,7 +5245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>60</v>
       </c>
@@ -5270,7 +5274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>61</v>
       </c>
@@ -5299,7 +5303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>61</v>
       </c>
@@ -5328,7 +5332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>61</v>
       </c>
@@ -5357,7 +5361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>62</v>
       </c>
@@ -5386,7 +5390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>63</v>
       </c>
@@ -5415,7 +5419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>9</v>
       </c>
@@ -5444,7 +5448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>16</v>
       </c>
@@ -5473,7 +5477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>17</v>
       </c>
@@ -5502,7 +5506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>11</v>
       </c>
@@ -5531,7 +5535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>12</v>
       </c>
@@ -5560,7 +5564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>13</v>
       </c>
@@ -5589,7 +5593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>14</v>
       </c>
@@ -5618,7 +5622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>15</v>
       </c>
@@ -5647,7 +5651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>11</v>
       </c>
@@ -5676,7 +5680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>12</v>
       </c>
@@ -5705,7 +5709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>13</v>
       </c>
@@ -5734,7 +5738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>14</v>
       </c>
@@ -5763,7 +5767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>15</v>
       </c>
@@ -5792,7 +5796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>9</v>
       </c>
@@ -5821,7 +5825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>75</v>
       </c>
@@ -5850,7 +5854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>76</v>
       </c>
@@ -5879,7 +5883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>11</v>
       </c>
@@ -5908,7 +5912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>77</v>
       </c>
@@ -6807,7 +6811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>11</v>
       </c>
@@ -6836,7 +6840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>12</v>
       </c>
@@ -6865,7 +6869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>13</v>
       </c>
@@ -6894,7 +6898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>14</v>
       </c>
@@ -6923,7 +6927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>15</v>
       </c>
@@ -6952,7 +6956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>108</v>
       </c>
@@ -6981,7 +6985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>109</v>
       </c>
@@ -7010,7 +7014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>110</v>
       </c>
@@ -7039,7 +7043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>111</v>
       </c>
@@ -7068,7 +7072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>111</v>
       </c>
@@ -7097,7 +7101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>111</v>
       </c>
@@ -7126,7 +7130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>111</v>
       </c>
@@ -7155,7 +7159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>112</v>
       </c>
@@ -7184,7 +7188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>112</v>
       </c>
@@ -7213,7 +7217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>112</v>
       </c>
@@ -7242,7 +7246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>113</v>
       </c>
@@ -7271,7 +7275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>113</v>
       </c>
@@ -7300,7 +7304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>114</v>
       </c>
@@ -7329,7 +7333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>115</v>
       </c>
@@ -7358,7 +7362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>116</v>
       </c>
@@ -7387,7 +7391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>117</v>
       </c>
@@ -7416,7 +7420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>118</v>
       </c>
@@ -7445,7 +7449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>119</v>
       </c>
@@ -7474,7 +7478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>120</v>
       </c>
@@ -7503,7 +7507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>121</v>
       </c>
@@ -7532,7 +7536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>122</v>
       </c>
@@ -7561,7 +7565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>123</v>
       </c>
@@ -7590,7 +7594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>124</v>
       </c>
@@ -7619,7 +7623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>125</v>
       </c>
@@ -7648,7 +7652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>126</v>
       </c>
@@ -7677,7 +7681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>127</v>
       </c>
@@ -7706,7 +7710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>128</v>
       </c>
@@ -7735,7 +7739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>129</v>
       </c>
@@ -7764,7 +7768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>130</v>
       </c>
@@ -7793,7 +7797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>121</v>
       </c>
@@ -7822,7 +7826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>122</v>
       </c>
@@ -7851,7 +7855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>123</v>
       </c>
@@ -7880,7 +7884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>75</v>
       </c>
@@ -7909,7 +7913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>76</v>
       </c>
@@ -7938,7 +7942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>11</v>
       </c>
@@ -7967,7 +7971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>77</v>
       </c>
@@ -7996,7 +8000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>131</v>
       </c>
@@ -8025,7 +8029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>132</v>
       </c>
@@ -8054,7 +8058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>9</v>
       </c>
@@ -8083,7 +8087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>16</v>
       </c>
@@ -8112,7 +8116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>17</v>
       </c>
@@ -8141,7 +8145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>133</v>
       </c>
@@ -8170,7 +8174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>134</v>
       </c>
@@ -8199,7 +8203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>75</v>
       </c>
@@ -8228,7 +8232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>76</v>
       </c>
@@ -8257,7 +8261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>11</v>
       </c>
@@ -8286,7 +8290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>77</v>
       </c>
@@ -8315,7 +8319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>75</v>
       </c>
@@ -8344,7 +8348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>76</v>
       </c>
@@ -8373,7 +8377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>11</v>
       </c>
@@ -8402,7 +8406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>77</v>
       </c>
@@ -8431,7 +8435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>11</v>
       </c>
@@ -8460,7 +8464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>12</v>
       </c>
@@ -8489,7 +8493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>13</v>
       </c>
@@ -8518,7 +8522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>14</v>
       </c>
@@ -8547,7 +8551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>15</v>
       </c>
@@ -8577,6 +8581,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I252" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="1"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>